--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:16</t>
+    <t xml:space="preserve">2026-09-29 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:04</t>
+    <t xml:space="preserve">2026-09-29 18:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>81.01</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>68.93</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="5">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:43</t>
+    <t xml:space="preserve">2026-10-05 04:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -513,7 +513,7 @@
         <v>18.57</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>74.18</v>
+        <v>74.19</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>55.62</v>
@@ -530,7 +530,7 @@
         <v>81.01</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>68.92</v>
+        <v>68.93</v>
       </c>
     </row>
     <row r="5">
